--- a/prices/prices.xlsx
+++ b/prices/prices.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="CONCRETE" sheetId="1" r:id="rId1"/>
@@ -121,15 +121,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -437,112 +434,112 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>3774</v>
+      <c r="B2">
+        <v>4152</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3">
-        <v>4002</v>
+      <c r="B3">
+        <v>4404</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
-        <v>4074</v>
+      <c r="B4">
+        <v>4482</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
-        <v>4296</v>
+      <c r="B5">
+        <v>4728</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3">
-        <v>4471</v>
+      <c r="B6">
+        <v>4918</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3">
-        <v>4539</v>
+      <c r="B7">
+        <v>5004</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3">
-        <v>4935</v>
+      <c r="B8">
+        <v>5430</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3">
-        <v>3909</v>
+      <c r="B9">
+        <v>4302</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3">
-        <v>4209</v>
+      <c r="B10">
+        <v>4632</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3">
-        <v>4299</v>
+      <c r="B11">
+        <v>4740</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3">
-        <v>4539</v>
+      <c r="B12">
+        <v>5004</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3">
-        <v>4746</v>
+      <c r="B13">
+        <v>5221</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="3">
-        <v>4827</v>
+      <c r="B14">
+        <v>5310</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3">
-        <v>5055</v>
+      <c r="B15">
+        <v>5562</v>
       </c>
     </row>
     <row r="26" spans="3:3" x14ac:dyDescent="0.3">
@@ -563,6 +560,7 @@
   <cols>
     <col min="1" max="1" width="17.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -577,528 +575,528 @@
       <c r="A2" s="1">
         <v>5</v>
       </c>
-      <c r="B2" s="5">
-        <v>454.68</v>
+      <c r="B2" s="4">
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>6</v>
       </c>
-      <c r="B3" s="5">
-        <v>467.1</v>
+      <c r="B3" s="4">
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>7</v>
       </c>
-      <c r="B4" s="5">
-        <v>479.58</v>
+      <c r="B4" s="4">
+        <v>528</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>8</v>
       </c>
-      <c r="B5" s="5">
-        <v>492.78</v>
+      <c r="B5" s="4">
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>9</v>
       </c>
-      <c r="B6" s="5">
-        <v>506.1</v>
+      <c r="B6" s="4">
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>10</v>
       </c>
-      <c r="B7" s="5">
-        <v>517.98</v>
+      <c r="B7" s="4">
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>11</v>
       </c>
-      <c r="B8" s="5">
-        <v>531.48</v>
+      <c r="B8" s="4">
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>12</v>
       </c>
-      <c r="B9" s="5">
-        <v>544.38</v>
+      <c r="B9" s="4">
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>13</v>
       </c>
-      <c r="B10" s="5">
-        <v>556.67999999999995</v>
+      <c r="B10" s="4">
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>14</v>
       </c>
-      <c r="B11" s="5">
-        <v>570</v>
+      <c r="B11" s="4">
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>15</v>
       </c>
-      <c r="B12" s="5">
-        <v>582.78</v>
+      <c r="B12" s="4">
+        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>16</v>
       </c>
-      <c r="B13" s="5">
-        <v>597.6</v>
+      <c r="B13" s="4">
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>17</v>
       </c>
-      <c r="B14" s="5">
-        <v>611.70000000000005</v>
+      <c r="B14" s="4">
+        <v>673</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>18</v>
       </c>
-      <c r="B15" s="5">
-        <v>627</v>
+      <c r="B15" s="4">
+        <v>690</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>19</v>
       </c>
-      <c r="B16" s="5">
-        <v>640.5</v>
+      <c r="B16" s="4">
+        <v>705</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>20</v>
       </c>
-      <c r="B17" s="5">
-        <v>654.9</v>
+      <c r="B17" s="4">
+        <v>720</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>21</v>
       </c>
-      <c r="B18" s="5">
-        <v>669.48</v>
+      <c r="B18" s="4">
+        <v>736</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>22</v>
       </c>
-      <c r="B19" s="5">
-        <v>683.7</v>
+      <c r="B19" s="4">
+        <v>752</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>23</v>
       </c>
-      <c r="B20" s="5">
-        <v>698.1</v>
+      <c r="B20" s="4">
+        <v>768</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>24</v>
       </c>
-      <c r="B21" s="5">
-        <v>713.58</v>
+      <c r="B21" s="4">
+        <v>785</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>25</v>
       </c>
-      <c r="B22" s="5">
-        <v>727.5</v>
+      <c r="B22" s="4">
+        <v>800</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>26</v>
       </c>
-      <c r="B23" s="5">
-        <v>742.08</v>
+      <c r="B23" s="4">
+        <v>816</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>27</v>
       </c>
-      <c r="B24" s="5">
-        <v>756.3</v>
+      <c r="B24" s="4">
+        <v>832</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>28</v>
       </c>
-      <c r="B25" s="5">
-        <v>771.48</v>
+      <c r="B25" s="4">
+        <v>849</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>29</v>
       </c>
-      <c r="B26" s="5">
-        <v>786.18</v>
+      <c r="B26" s="4">
+        <v>865</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>30</v>
       </c>
-      <c r="B27" s="5">
-        <v>799.8</v>
+      <c r="B27" s="4">
+        <v>880</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>31</v>
       </c>
-      <c r="B28" s="5">
-        <v>814.38</v>
+      <c r="B28" s="4">
+        <v>896</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>32</v>
       </c>
-      <c r="B29" s="5">
-        <v>828.9</v>
+      <c r="B29" s="4">
+        <v>912</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>33</v>
       </c>
-      <c r="B30" s="5">
-        <v>843</v>
+      <c r="B30" s="4">
+        <v>927</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>34</v>
       </c>
-      <c r="B31" s="5">
-        <v>857.88</v>
+      <c r="B31" s="4">
+        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>35</v>
       </c>
-      <c r="B32" s="5">
-        <v>872.1</v>
+      <c r="B32" s="4">
+        <v>959</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>36</v>
       </c>
-      <c r="B33" s="5">
-        <v>886.68</v>
+      <c r="B33" s="4">
+        <v>975</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>37</v>
       </c>
-      <c r="B34" s="5">
-        <v>901.2</v>
+      <c r="B34" s="4">
+        <v>991</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>38</v>
       </c>
-      <c r="B35" s="5">
-        <v>915.3</v>
+      <c r="B35" s="4">
+        <v>1007</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>39</v>
       </c>
-      <c r="B36" s="5">
-        <v>930.48</v>
+      <c r="B36" s="4">
+        <v>1024</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>40</v>
       </c>
-      <c r="B37" s="5">
-        <v>943.98</v>
+      <c r="B37" s="4">
+        <v>1039</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>41</v>
       </c>
-      <c r="B38" s="5">
-        <v>959.28</v>
+      <c r="B38" s="4">
+        <v>1055</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>42</v>
       </c>
-      <c r="B39" s="5">
-        <v>973.68</v>
+      <c r="B39" s="4">
+        <v>1071</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>43</v>
       </c>
-      <c r="B40" s="5">
-        <v>987.9</v>
+      <c r="B40" s="4">
+        <v>1087</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>44</v>
       </c>
-      <c r="B41" s="5">
-        <v>1003.08</v>
+      <c r="B41" s="4">
+        <v>1103</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45</v>
       </c>
-      <c r="B42" s="5">
-        <v>1017.6</v>
+      <c r="B42" s="4">
+        <v>1119</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46</v>
       </c>
-      <c r="B43" s="5">
-        <v>1032</v>
+      <c r="B43" s="4">
+        <v>1135</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>47</v>
       </c>
-      <c r="B44" s="5">
-        <v>1046.28</v>
+      <c r="B44" s="4">
+        <v>1151</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>48</v>
       </c>
-      <c r="B45" s="5">
-        <v>1060.98</v>
+      <c r="B45" s="4">
+        <v>1167</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>49</v>
       </c>
-      <c r="B46" s="5">
-        <v>1075.5</v>
+      <c r="B46" s="4">
+        <v>1183</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>50</v>
       </c>
-      <c r="B47" s="5">
-        <v>1090.08</v>
+      <c r="B47" s="4">
+        <v>1199</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+      <c r="A48" s="3">
         <v>51</v>
       </c>
       <c r="B48" s="1">
-        <v>1113</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="4">
+      <c r="A49" s="3">
         <v>52</v>
       </c>
       <c r="B49" s="1">
-        <v>1134</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+      <c r="A50" s="3">
         <v>53</v>
       </c>
       <c r="B50" s="1">
-        <v>1155</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="A51" s="3">
         <v>54</v>
       </c>
       <c r="B51" s="1">
-        <v>1178</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="A52" s="3">
         <v>55</v>
       </c>
       <c r="B52" s="1">
-        <v>1200</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="A53" s="3">
         <v>56</v>
       </c>
       <c r="B53" s="1">
-        <v>1221</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="A54" s="3">
         <v>57</v>
       </c>
       <c r="B54" s="1">
-        <v>1244</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="A55" s="3">
         <v>58</v>
       </c>
       <c r="B55" s="1">
-        <v>1265</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="A56" s="3">
         <v>59</v>
       </c>
       <c r="B56" s="1">
-        <v>1288</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="A57" s="3">
         <v>60</v>
       </c>
       <c r="B57" s="1">
-        <v>1309</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="A58" s="3">
         <v>61</v>
       </c>
       <c r="B58" s="1">
-        <v>1331</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="A59" s="3">
         <v>62</v>
       </c>
       <c r="B59" s="1">
-        <v>1356</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="4">
+      <c r="A60" s="3">
         <v>63</v>
       </c>
       <c r="B60" s="1">
-        <v>1374</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="4">
+      <c r="A61" s="3">
         <v>64</v>
       </c>
       <c r="B61" s="1">
-        <v>1396</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="4">
+      <c r="A62" s="3">
         <v>65</v>
       </c>
       <c r="B62" s="1">
-        <v>1419</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+      <c r="A63" s="3">
         <v>66</v>
       </c>
       <c r="B63" s="1">
-        <v>1440</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="A64" s="3">
         <v>67</v>
       </c>
       <c r="B64" s="1">
-        <v>1463</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="A65" s="3">
         <v>68</v>
       </c>
       <c r="B65" s="1">
-        <v>1484</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="A66" s="3">
         <v>69</v>
       </c>
       <c r="B66" s="1">
-        <v>1506</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="A67" s="3">
         <v>70</v>
       </c>
       <c r="B67" s="1">
-        <v>1528</v>
+        <v>1680</v>
       </c>
     </row>
   </sheetData>
